--- a/phase1_analysis/data/BD2025_sched_subset.xlsx
+++ b/phase1_analysis/data/BD2025_sched_subset.xlsx
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="D36">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="D49">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="D53">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="D55">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="D62">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="D65">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="D68">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="D70">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D71">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="D76">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="D77">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="D78">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="D79">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D80">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="D81">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="D82">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D83">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="D85">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="D88">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="D89">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D91">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="D92">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="D93">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="D94">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D95">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="D96">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="D97">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="D100">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="D102">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="103">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D103">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105">
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="D105">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="D107">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D108">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="D109">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="110">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="D110">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="D111">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="D112">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113">
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="D113">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D114">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D115">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="116">
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="D116">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="D117">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118">
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="D118">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="D119">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="121">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D122">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="124">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="125">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="127">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128">
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="D128">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="129">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D129">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="130">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="131">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="D131">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="132">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="D133">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="134">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D137">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="139">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="140">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="D140">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="141">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="143">
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D143">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="144">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="D144">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="145">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="D145">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="146">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="D146">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147">
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="D147">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="148">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="D149">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="150">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="151">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="D151">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="152">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="D152">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="153">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="154">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="155">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="156">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="157">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="158">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="159">
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="160">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="161">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="162">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="163">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="D163">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="164">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D164">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="165">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="D165">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="166">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="D166">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="167">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="D167">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="168">
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="D168">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="169">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="170">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="171">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="D172">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="173">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="D173">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="174">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="176">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177">
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="D177">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="178">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="179">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="180">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="181">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="D181">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="182">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183">
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184">
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="185">
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
